--- a/Config/Excels/__enums__.xlsx
+++ b/Config/Excels/__enums__.xlsx
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:XFD48"/>
+  <dimension ref="A1:XFD46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="17.125" customWidth="1" style="7" min="1" max="1"/>
@@ -19332,7 +19332,6 @@
       <c r="L46" s="23" t="n"/>
     </row>
     <row r="47" customFormat="1" s="20"/>
-    <row r="48"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
@@ -20593,362 +20592,691 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG4"/>
+  <dimension ref="A1:CV39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>flags</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>unique</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>*items</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="H2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>是否为位标记枚举</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>枚举项是否唯一</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>枚举名</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>别名</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>语言类型</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ELanguage</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" t="b">
+      <c r="E4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>aot</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Unspecified</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>未指定</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>未指定</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>ChineseSimplified</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>简体中文</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>ChineseTraditional</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>繁体中文</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>英语</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>French</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>法语</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG4" s="3" t="inlineStr">
         <is>
           <t>German</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" s="3" t="inlineStr">
         <is>
           <t>德语</t>
         </is>
       </c>
-      <c r="AI4" t="n">
+      <c r="AI4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AL4" s="3" t="inlineStr">
         <is>
           <t>Indonesian</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AM4" s="3" t="inlineStr">
         <is>
           <t>印尼语</t>
         </is>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AQ4" s="3" t="inlineStr">
         <is>
           <t>Italian</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr">
         <is>
           <t>意大利语</t>
         </is>
       </c>
-      <c r="AS4" t="n">
+      <c r="AS4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
         <is>
           <t>Japanese</t>
         </is>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>日语</t>
         </is>
       </c>
-      <c r="AX4" t="n">
+      <c r="AX4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BA4" s="3" t="inlineStr">
         <is>
           <t>Korean</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BB4" s="3" t="inlineStr">
         <is>
           <t>韩语</t>
         </is>
       </c>
-      <c r="BC4" t="n">
+      <c r="BC4" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BF4" s="3" t="inlineStr">
         <is>
           <t>PortugueseBrazil</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BG4" s="3" t="inlineStr">
         <is>
           <t>葡萄牙语(巴西)</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BH4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BK4" s="3" t="inlineStr">
         <is>
           <t>PortuguesePortugal</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BL4" s="3" t="inlineStr">
         <is>
           <t>葡萄牙语(葡萄牙)</t>
         </is>
       </c>
-      <c r="BM4" t="n">
+      <c r="BM4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BP4" s="3" t="inlineStr">
         <is>
           <t>Russian</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BQ4" s="3" t="inlineStr">
         <is>
           <t>俄语</t>
         </is>
       </c>
-      <c r="BR4" t="n">
+      <c r="BR4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BU4" s="3" t="inlineStr">
         <is>
           <t>Spanish</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BV4" s="3" t="inlineStr">
         <is>
           <t>西班牙语</t>
         </is>
       </c>
-      <c r="BW4" t="n">
+      <c r="BW4" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="BZ4" s="3" t="inlineStr">
         <is>
           <t>Thai</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CA4" s="3" t="inlineStr">
         <is>
           <t>泰语</t>
         </is>
       </c>
-      <c r="CB4" t="n">
+      <c r="CB4" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CE4" s="3" t="inlineStr">
         <is>
           <t>Vietnamese</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CF4" s="3" t="inlineStr">
         <is>
           <t>越南语</t>
         </is>
       </c>
-      <c r="CG4" t="n">
+      <c r="CG4" s="3" t="n">
         <v>15</v>
       </c>
     </row>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChineseSimplified</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>简体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChineseTraditional</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>繁体中文</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>繁体中文</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>英语</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>French</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>法语</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>法语</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>German</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>德语</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>德语</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Indonesian</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>印尼语</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>印尼语</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Italian</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>意大利语</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>意大利语</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>日语</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>日语</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>韩语</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>韩语</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PortugueseBrazil</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>葡萄牙语(巴西)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>葡萄牙语(巴西)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PortuguesePortugal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>葡萄牙语(葡萄牙)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>葡萄牙语(葡萄牙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Russian</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>俄语</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>12</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>俄语</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>西班牙语</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>西班牙语</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Thai</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>泰语</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>14</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>泰语</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>越南语</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>越南语</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>